--- a/DateBase/orders/Dang Nguyen48_2026-10-8.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-8.xlsx
@@ -811,6 +811,9 @@
       <c r="G2" t="str">
         <v>08856105510101510510141051015553025655101055101053020203030</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
